--- a/public/templates/forms/A-083-RiskFindingRegister-FORM.xlsx
+++ b/public/templates/forms/A-083-RiskFindingRegister-FORM.xlsx
@@ -20,7 +20,7 @@
   <numFmts count="0"/>
   <fonts count="14">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -333,7 +333,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -367,7 +367,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/forms/A-083-RiskFindingRegister-FORM.xlsx
+++ b/public/templates/forms/A-083-RiskFindingRegister-FORM.xlsx
@@ -4,20 +4,25 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Column Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="0">Form!$14:$14</definedName>
+  </definedNames>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="14">
     <font>
       <name val="Aptos"/>
@@ -157,7 +162,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -213,6 +218,9 @@
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -577,7 +585,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -736,7 +744,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="32" customHeight="1">
+    <row r="14" ht="34.7" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
           <t>Finding ID</t>
@@ -947,7 +955,6 @@
       </c>
       <c r="C29" s="11">
         <f>COUNTA(A15:A26)</f>
-        <v/>
       </c>
     </row>
     <row r="30">
@@ -958,7 +965,6 @@
       </c>
       <c r="C30" s="11">
         <f>COUNTIF(I15:I26,"Open")</f>
-        <v/>
       </c>
     </row>
     <row r="31">
@@ -969,7 +975,6 @@
       </c>
       <c r="C31" s="11">
         <f>COUNTIF(I15:I26,"In Progress")</f>
-        <v/>
       </c>
     </row>
     <row r="32">
@@ -980,7 +985,6 @@
       </c>
       <c r="C32" s="11">
         <f>COUNTIFS(H15:H26,"&lt;"&amp;TODAY(),I15:I26,"Open")+COUNTIFS(H15:H26,"&lt;"&amp;TODAY(),I15:I26,"In Progress")</f>
-        <v/>
       </c>
     </row>
     <row r="33">
@@ -991,7 +995,6 @@
       </c>
       <c r="C33" s="11">
         <f>COUNTIF(I15:I26,"Risk Accepted")</f>
-        <v/>
       </c>
     </row>
     <row r="34">
@@ -1002,7 +1005,6 @@
       </c>
       <c r="C34" s="11">
         <f>COUNTIF(I15:I26,"Closed")</f>
-        <v/>
       </c>
     </row>
     <row r="35">
@@ -1139,7 +1141,7 @@
     <row r="51" ht="70" customHeight="1">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>Drafter's note (internal, delete before publishing): This register absorbed retired A-082 (Remediation Tracking) and A-084 (Remediation Assignment / Due Date), so it carries full remediation-tracking duty. Impact Rank intentionally weights life-safety and service-continuity over generic severity, per Scoping Notes. NENA citations map to §3.2 (compliance action plan / documented risk acceptance), §4.3 (risk treatment and reassessment cadence), and §5.2 (security-assessment findings).</t>
+          <t>Drafter's note (internal, delete before publishing): This register absorbed the retired Remediation Tracking and Remediation Assignment / Due Date registers, so it carries full remediation-tracking duty. Impact Rank intentionally weights life-safety and service-continuity over generic severity, per Scoping Notes. NENA citations map to §3.2 (compliance action plan / documented risk acceptance), §4.3 (risk treatment and reassessment cadence), and §5.2 (security-assessment findings).</t>
         </is>
       </c>
       <c r="B51" s="17" t="n"/>
@@ -1191,7 +1193,8 @@
       <formula1>"Open,In Progress,Remediated,Risk Accepted,Closed"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>
 
@@ -1199,7 +1202,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1246,7 +1249,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="34.7" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
           <t>Finding ID</t>
@@ -1268,7 +1271,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="30" customHeight="1">
+    <row r="6" ht="34.7" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
           <t>Source (type + reference)</t>
@@ -1290,7 +1293,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="30" customHeight="1">
+    <row r="7" ht="34.7" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
           <t>Finding</t>
@@ -1312,7 +1315,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="34.7" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
           <t>Impact Rank</t>
@@ -1334,7 +1337,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="34.7" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
           <t>Risk Register Ref</t>
@@ -1356,7 +1359,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="30" customHeight="1">
+    <row r="10" ht="34.7" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
           <t>Owner (Role)</t>
@@ -1378,7 +1381,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="30" customHeight="1">
+    <row r="11" ht="34.7" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Remediation Action</t>
@@ -1400,7 +1403,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="34.7" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
           <t>Due Date</t>
@@ -1416,13 +1419,11 @@
           <t>Required</t>
         </is>
       </c>
-      <c r="D12" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-15</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="30" customHeight="1">
+      <c r="D12" s="24">
+        <v>46157</v>
+      </c>
+    </row>
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
           <t>Status</t>
@@ -1539,6 +1540,7 @@
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="B21:D21"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
 </worksheet>
 </file>